--- a/mlef_pipeline/results/OS_6/SQUAMOUS/RWD_DP/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/OS_6/SQUAMOUS/RWD_DP/rwd-only/results.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.74 ± 0.09</t>
+          <t>0.71 ± 0.09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
